--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92541321732</v>
+        <v>46157.93116370637</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93116370637</v>
+        <v>46157.93369340183</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93369340183</v>
+        <v>46157.93673664852</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93673664852</v>
+        <v>46158.28195351089</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28195351089</v>
+        <v>46158.29719564116</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29719564116</v>
+        <v>46158.29791929705</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29791929705</v>
+        <v>46158.33356823539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33356823539</v>
+        <v>46158.37211346101</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/22. ИП Норчак Евгений (аренда гаража)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37211346101</v>
+        <v>46158.37268303952</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
